--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0108.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0108.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Chỉ mục vượt quá phạm vi</t>
+          <t>Mục lục vượt quá phạm vi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Chỉ số vượt quá giới hạn</t>
+          <t>Mục lục vượt quá phạm vi</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Số lượng cấu hình vượt quá giới hạn</t>
+          <t>Số cấu hình vượt quá giới hạn.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Đã đạt số lần thao tác tối đa</t>
+          <t>Đã đạt số thao tác tối đa</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Có giai đoạn chưa hoàn tất</t>
+          <t>Có các giai đoạn chưa hoàn thiện</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Tham số thuộc tính Giấc Mơ không hợp lệ</t>
+          <t>Tham số thuộc tính giấc mơ không hợp lệ</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Độ dài Khối Giấc Mơ ban đầu vượt quá giới hạn</t>
+          <t>Độ dài Khối Giấc Mơ Ban Đầu vượt quá giới hạn</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Độ dài Echo ban đầu vượt quá giới hạn</t>
+          <t>Độ dài Tiếng Vọng Ban Đầu vượt quá giới hạn</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Giai đoạn không tồn tại</t>
+          <t>Sân khấu không tồn tại.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Đã hoàn tất Tuyển dụng Echo</t>
+          <t>Hoàn Tất Tuyển Chọn Tần Số</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Echo không nằm trong Tuyển dụng Echo</t>
+          <t>Echo không có trong Danh sách Chiêu mộ Echo</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Tạo Echo thất bại</t>
+          <t>Không tạo được Echo</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Insufficient Dreamland Couponss</t>
+          <t>Phiếu Giấc Mơ không đủ.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Giai đoạn chưa hoàn tất</t>
+          <t>Giai đoạn chưa hoàn thiện</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Mặt hàng trong cửa hàng không tồn tại</t>
+          <t>Mặt hàng không tồn tại</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Insufficient Frequency Crystals</t>
+          <t>Pha lê Tần số không đủ</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Số lượng vật phẩm vượt quá giới hạn</t>
+          <t>Số lượng vật phẩm đã vượt quá giới hạn</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Tạo vật phẩm thất bại</t>
+          <t>Không tạo được vật phẩm</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Hộp Giấc Mơ không tồn tại</t>
+          <t>Hộp Mộng không tồn tại</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Hộp Giấc Mơ không tồn tại</t>
+          <t>Hộp Mộng không tồn tại</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Hộp Giấc Mơ không tồn tại</t>
+          <t>Hộp Mộng không tồn tại</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Lỗi Phúc Lành</t>
+          <t>Lỗi phước lành</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Sử dụng Phúc Lành vượt quá giới hạn</t>
+          <t>Đã vượt quá giới hạn sử dụng Phúc Lành</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Lỗi Phúc Lành</t>
+          <t>Lỗi phước lành</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Sử dụng Phúc Lành thất bại</t>
+          <t>Không thể sử dụng Phúc Lành</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Chế độ Vô Hạn không được phép</t>
+          <t>Chế độ vô hạn không được phép</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Phúc Lành bị khóa</t>
+          <t>Phước lành bị khóa</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Giai đoạn bị khóa</t>
+          <t>Sân khấu bị khóa.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Hợp nhất ngay</t>
+          <t>Hợp thể ngay đi</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Returned Materials</t>
+          <t>Nguyên liệu đã trả lại</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Sigil Refreshing Failed</t>
+          <t>Làm Mới Ấn Tín Thất Bại</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Sigil List Empty</t>
+          <t>Danh Sách Ấn Tín Trống</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Sigil Log Incorrect</t>
+          <t>Nhật Ký Ấn Tín Không Chính Xác</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Through the Sea Thou Break" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Vượt Qua Biển Cả" để mở khóa</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Through the Sea Thou Break" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Vượt Qua Biển Cả" để mở khóa</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình thử thách</t>
+          <t>Không tìm thấy cấu hình thử thách.</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Đã nhận phần thưởng</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Chưa mở khóa</t>
+          <t>Chưa khả dụng</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Exit Co-op Mode</t>
+          <t>Thoát Chế Độ Hợp Tác</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Ở lại Chế độ Co-op</t>
+          <t>Ở lại Chế độ Hợp tác</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Refresh</t>
+          <t>Làm mới</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Ẩn đến bản cập nhật phiên bản tiếp theo</t>
+          <t>Ẩn đến bản cập nhật tiếp theo</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Version Update</t>
+          <t>Cập Nhật Phiên Bản</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Version Update</t>
+          <t>Cập Nhật Phiên Bản</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Bắt đầu Mô phỏng</t>
+          <t>Bắt Đầu Mô Phỏng</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Tăng cường</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Chưa hoàn thành giai đoạn trước</t>
+          <t>Giai đoạn trước chưa được hoàn thành.</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Phá hủy đơn vị thử nghiệm trong Nhiệm vụ Chính "Shadow of Glory"</t>
+          <t>Hủy bỏ đơn vị thí nghiệm trong Nhiệm Vụ Chính "Bóng Tối Vinh Quang"</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Không tìm thấy phiên bản dữ liệu tùy chỉnh đơn hàng</t>
+          <t>Không tìm thấy phiên bản dữ liệu tùy chỉnh của Lệnh</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Kích hoạt trong Chế độ Hiển thị Hình ảnh</t>
+          <t>Kích hoạt ở Chế Độ Hiển Thị Hình Ảnh.</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Thay đổi Cài đặt</t>
+          <t>Thay Đổi Cài Đặt</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và hoàn thành Chương II Prologue của Nhiệm vụ Chính để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và hoàn thành Lời Mở Đầu Chương II trong Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Chính "Through the Sea Thou Break" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Vượt Qua Biển Cả" để mở khóa</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm vụ Chính "Shadow of Glory"</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và hoàn thành Nhiệm Vụ Chính "Bóng Tối Của Vinh Quang"</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Chính "Shadow of Glory"</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Bóng Tối Của Vinh Quang"</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Sự kiện không khả dụng</t>
+          <t>Sự kiện chưa khả dụng</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Thiếu dữ liệu chiến đấu</t>
+          <t>Dữ liệu trận đấu bị thiếu</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Cấu hình không tồn tại</t>
+          <t>Cấu hình không tồn tại.</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Chưa hoàn thành giai đoạn trước</t>
+          <t>Giai đoạn trước chưa được hoàn thành.</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Không thể lấy dữ liệu chiến đấu</t>
+          <t>Không thể truy xuất dữ liệu chiến đấu</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Không thể hoàn tác trạng thái nhận thưởng</t>
+          <t>Trạng thái nhận phần thưởng không thể hoàn tác</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Resonator cần thiết không có trong đội hình</t>
+          <t>Resonator yêu cầu không có trong đội hình</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Cấu hình trang thưởng không tồn tại</t>
+          <t>Không tìm thấy cấu hình trang phần thưởng</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Tham số nhận thưởng lỗi</t>
+          <t>Lỗi tham số khi nhận phần thưởng</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Reconnect</t>
+          <t>Kết Nối Lại</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử thách "Khu Vực Ổn Định" trong Tháp Nghịch Cảnh để mở khóa</t>
+          <t>Hoàn thành thử thách "Khu Vực Ổn Định" tại Tháp Nghịch Cảnh để mở khóa</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử thách "Khu Vực Thí Nghiệm" trong Tháp Nghịch Cảnh để mở khóa</t>
+          <t>Hoàn thành thử thách "Khu Vực Thí Nghiệm" tại Tháp Nghịch Cảnh để mở khóa</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương III Hồi III "Ngôi Sao Viễn Du" trong Nhiệm Vụ Chính để mở khóa</t>
+          <t>Hoàn thành Chương III Hồi III "Ngôi Sao Lang Thang Xa Xôi" trong Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Sau khi Lễ Kỷ Niệm bắt đầu, hãy tìm "cô ấy" trên đỉnh Rabelle College</t>
+          <t>Khi Lễ kỷ niệm bắt đầu, hãy tìm "cô ấy" trên đỉnh Rabelle College.</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Vui lòng hoàn thành Nhiệm Vụ Thám Hiểm "Đến Vùng Đất Nghịch Lý" trước</t>
+          <t>Hãy hoàn thành Nhiệm Vụ Thám Hiểm "Vào Vùng Đất Nghịch Lý" trước đã.</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử thách "Vùng Nước Cấm" tại Whimpering Wastes để mở khóa</t>
+          <t>Hoàn thành Thử Thách "Vùng Nước Cấm" tại Vùng Đất Than Khóc để mở khóa</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử thách "Khu Vực Ổn Định" trong Tháp Nghịch Cảnh</t>
+          <t>Hoàn thành thử thách "Khu Vực Ổn Định" tại Tháp Nghịch Cảnh</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử thách "Khu Vực Thí Nghiệm" trong Tháp Nghịch Cảnh</t>
+          <t>Hoàn thành thử thách "Khu Vực Thí Nghiệm" tại Tháp Nghịch Cảnh</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương III Hồi III "Ngôi Sao Viễn Du" trong Nhiệm Vụ Chính để mở khóa</t>
+          <t>Hoàn thành Chương III Hồi III "Ngôi Sao Lang Thang Xa Xôi" trong Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 5</t>
+          <t>Đạt Cấp Độ Liên Minh 5</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử thách "Vùng Nước Cấm" tại Whimpering Wastes</t>
+          <t>Hoàn thành Thử Thách "Vùng Nước Cấm" tại Vùng Đất Than Khóc</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Quit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Lưu</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Assets Missing</t>
+          <t>Thiếu Tài Nguyên</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Download Complete</t>
+          <t>Tải Hoàn Tất</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Wheel</t>
+          <t>Bánh Xe</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Solaris's Pole: Lahai-Roi</t>
+          <t>Cực của Solaris: Lahai-Roi</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Discord Nests: Lahai-Roi</t>
+          <t>Tổ Tacet Discord: Lahai-Roi</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Discord Nests</t>
+          <t>Các Tổ Tacet Discord</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Tacet Discords</t>
+          <t>Các Tacet Discord</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Phần thưởng Tinh Thể Tàn Dư</t>
+          <t>Các Phần Thưởng Pha Lê Tàn Tích</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Bỏ qua Hướng dẫn?</t>
+          <t>Bỏ qua Hướng Dẫn?</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Stay</t>
+          <t>Ở lại nào</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Bỏ qua</t>
+          <t>Bỏ Qua</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Echo skin configuration does not exist</t>
+          <t>Cấu hình trang phục Echo không tồn tại</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Echo skin not available</t>
+          <t>Trang phục Echo không khả dụng</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Echo interaction not available</t>
+          <t>Không thể tương tác với Echo</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Echo Thư viện not available</t>
+          <t>Bộ Sưu Tập Cộng Hưởng chưa mở khóa</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Số lượng Echo trang bị không khớp với cấu hình</t>
+          <t>Số Echo trang bị không khớp với cấu hình.</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Hành động giao diện Echo bị trùng lặp</t>
+          <t>Hành động ngoại hình Echo bị trùng lặp</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Echo không thể hiển thị trong danh sách</t>
+          <t>Không thể hiển thị Echo trong danh sách</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Cấu hình nút không tồn tại</t>
+          <t>Cấu hình điểm nút không tồn tại</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Nút không có dữ liệu</t>
+          <t>Điểm nút không có dữ liệu</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Nút không khả dụng</t>
+          <t>Điểm nút không khả dụng</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Node not in reward status</t>
+          <t>Điểm nút chưa ở trạng thái nhận thưởng</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Nút đã được sửa chữa</t>
+          <t>Điểm nút đã được sửa xong</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Nút đã hoàn thành</t>
+          <t>Điểm nút hoàn tất</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Trạng thái nút không chính xác</t>
+          <t>Trạng thái nút không đúng</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Lỗi cập nhật nút</t>
+          <t>Lỗi cập nhật điểm nút</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Chỉ số mảng nút yêu cầu vượt quá giới hạn</t>
+          <t>Chỉ mục mảng nút yêu cầu vượt quá giới hạn</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11354,8 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Shell Credits đạt giới hạn tối đa sau khi trao đổi
-*(Các dòng giữ nguyên theo quy tắc tên riêng/ thuật ngữ hệ thống:)*</t>
+          <t>Shell Credit đạt giới hạn tối đa sau khi trao đổi</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11495,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Cấu hình sự kiện chưa xác định</t>
+          <t>Cấu hình sự kiện không xác định.</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11565,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Không tìm thấy phiên bản thành phần</t>
+          <t>Không xác định được phiên bản linh kiện</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11845,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Lỗi yêu cầu phần thưởng</t>
+          <t>Lỗi phần thưởng yêu cầu</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11915,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Cấu hình bản ghi sự kiện chưa xác định</t>
+          <t>Cấu hình ghi nhận sự kiện không xác định</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12055,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Trạng thái nhận phần thưởng bất thường</t>
+          <t>Trạng thái nhận thưởng bất thường.</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12125,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Chỉ số mảng phần thưởng bị trùng lặp</t>
+          <t>Chỉ mục phần thưởng bị trùng lặp</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12195,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Cấu hình phần thưởng chưa xác định</t>
+          <t>Cấu hình phần thưởng không xác định</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12265,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Đóng gói giai đoạn thất bại</t>
+          <t>Không đóng gói được giai đoạn</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12335,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Giai đoạn trước chưa hoàn thành</t>
+          <t>Giai đoạn trước chưa hoàn tất</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12405,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Tăng tốc! Bolt &amp; Blitz!</t>
+          <t>Tốc Lực Tối Đa! Sấm Chớp &amp; Tia Lửa!</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12475,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Save Feature</t>
+          <t>Lưu Tính Năng</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12545,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Re-Login</t>
+          <t>Đăng Nhập Lại</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12615,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình thay thế cho vật phẩm có thể tiêu hao</t>
+          <t>Không tìm thấy cấu hình thay thế cho vật phẩm tiêu hao</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12755,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Không thể thực hiện hành động này ở trạng thái hiện tại</t>
+          <t>Hiện không thể thực hiện hành động này</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12825,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Tài khoản người chơi đã bị xóa</t>
+          <t>Tài khoản người chơi đã được truy vấn đã bị xóa</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12895,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Thử thách đã đóng hoặc đang ở Chế độ Co-op</t>
+          <t>Thử thách đã đóng hoặc đang ở Chế độ Hợp tác</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13105,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Tải hành vi đối thủ thất bại</t>
+          <t>Không tải được hành vi đối thủ</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13175,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Loại thẻ không chính xác</t>
+          <t>Loại thẻ không đúng</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13245,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Loại sự kiện không chính xác</t>
+          <t>Loại sự kiện sai</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13315,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Loại sự kiện không đúng</t>
+          <t>Loại sự kiện sai</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13385,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn Domain</t>
+          <t>Đã đạt giới hạn Tổ Tacet</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13455,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn Novelties</t>
+          <t>Đã đạt giới hạn Vật phẩm Đặc Biệt</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13525,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Tham số không đúng</t>
+          <t>Thông số sai.</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13595,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Không có khu vực Triển khai khả dụng</t>
+          <t>Không có khu vực triển khai</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13805,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Lỗi ID sự kiện</t>
+          <t>Lỗi ID Sự kiện</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13875,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Lỗi cấu hình Domain</t>
+          <t>Lỗi cấu hình Tổ Tacet</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14085,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Bảng sự kiện hướng dẫn không tồn tại</t>
+          <t>Bảng Sự Kiện Hướng Dẫn Không Tồn Tại</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14295,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn triển khai Echo</t>
+          <t>Đã Đạt Giới Hạn Triệu Hồi Tiếng Vọng</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14365,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn triển khai Novelty</t>
+          <t>Đã đạt giới hạn triển khai Vật phẩm Đặc Biệt</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14435,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Thử thách đã được bỏ qua</t>
+          <t>Thử thách đã bị bỏ qua</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14505,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Motorbike Collab, không tìm thấy cấu hình chủ đề cộng tác</t>
+          <t>Hợp Tác Xe Máy, không tìm thấy cấu hình đối tượng hợp tác</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14575,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Motorbike Collab, không có phần thưởng để nhận</t>
+          <t>Hợp Tác Xe Máy, không có phần thưởng để nhận</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14715,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi nhận phần thưởng Giai đoạn 1 SOL3</t>
+          <t>Mở khóa sau khi nhận phần thưởng Giai Đoạn 1 SOL3.</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14785,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi nhận phần thưởng Giai đoạn 2 SOL3</t>
+          <t>Mở khóa sau khi nhận phần thưởng Giai Đoạn 2 SOL3.</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14855,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi nhận phần thưởng Giai đoạn 3 SOL3</t>
+          <t>Mở khóa sau khi nhận phần thưởng Giai Đoạn 3 SOL3.</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14925,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi nhận phần thưởng Giai đoạn 4 SOL3</t>
+          <t>Mở khóa sau khi nhận phần thưởng Giai Đoạn 4 SOL3.</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14995,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi nhận phần thưởng Giai đoạn 5 SOL3</t>
+          <t>Mở khóa sau khi nhận phần thưởng Giai Đoạn 5 SOL3.</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15065,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Thử Thách</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15135,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Không thể có nhiều hơn một Resonator Hỗ trợ trong đội</t>
+          <t>Bạn không thể có nhiều hơn một Resonator Hỗ Trợ trong đội.</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15205,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Không thể có các Resonator giống nhau trong đội</t>
+          <t>Bạn không thể có các Resonator trùng lặp trong đội.</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15275,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Thu thập ít nhất 24 Crest trong bất kỳ giai đoạn nào của Tower of Adversity: Hazard Zone</t>
+          <t>Thu thập ít nhất 24 Huy Hiệu trong bất kỳ giai đoạn nào của Tháp Nghịch Cảnh: Khu Vực Nguy Hiểm</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15345,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Hướng dẫn "Startorch Legends: The Matrix Intruder"</t>
+          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Huyền Thoại Sao Đầu Tiên: Kẻ Xâm Nhập Ma Trận"</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15415,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Smartprint Cube khởi động lại quá thường xuyên</t>
+          <t>Khối Smartprint Cube khởi động lại quá thường xuyên</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15485,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Không thể thay đổi Resonator Hỗ trợ trong trạng thái này</t>
+          <t>Không thể thay đổi Resonator Hỗ Trợ ở trạng thái này</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15555,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15625,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Lưu và Thoát</t>
+          <t>Lưu và thoát</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15695,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15765,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Lưu và Chuyển đổi</t>
+          <t>Lưu và chuyển đổi</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15835,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15905,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Lưu và Tiếp tục</t>
+          <t>Lưu và tiếp tục</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15975,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16255,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Khó</t>
+          <t>Khó khăn</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16325,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Tìm Exoswarm bị thất lạc</t>
+          <t>Tìm Exoswarm đã thất lạc.</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16535,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Chỉ số chính của Echo này không khớp</t>
+          <t>Chỉ số chính của Tổ Tacet này không khớp.</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16675,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Tham số truy vấn không hợp lệ</t>
+          <t>Các tham số truy vấn không hợp lệ</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16745,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Echo này không thể chỉnh sửa</t>
+          <t>Hồi Âm này không thể chỉnh sửa.</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16815,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Thay đổi chỉ số thất bại</t>
+          <t>Thay đổi thuộc tính thất bại</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16955,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Chưa đạt điểm thưởng</t>
+          <t>Chưa đạt điểm thưởng yêu cầu</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17025,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Phần thưởng đã được nhận</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17095,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Không thể kích hoạt Weekly Subscription nhiều lần</t>
+          <t>Không thể kích hoạt Gói Đăng Ký Hàng Tuần nhiều lần</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17165,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình Weekly Subscription</t>
+          <t>Không tìm thấy cấu hình Gói Đăng Ký Hàng Tuần</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17235,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Gói Đăng ký Hàng tuần chưa được kích hoạt</t>
+          <t>Gói Đăng Ký Hàng Tuần chưa kích hoạt</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17375,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Phần thưởng đã được nhận</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17445,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Gói Đăng ký Hàng tuần đã hết hạn</t>
+          <t>Gói Đăng Ký Hàng Tuần đã hết hạn</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17515,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Không có chỉ số để xác nhận</t>
+          <t>Không có chỉ số nào cần xác nhận</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17795,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Cấu hình thực thể hiển thị không tồn tại</t>
+          <t>Cấu hình hiển thị thực thể không tồn tại</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17865,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Cấu hình hiển thị Echo không tồn tại</t>
+          <t>Cấu hình Echo hiển thị không tồn tại</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17935,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Yêu cầu hiển thị thực thể bị trùng lặp</t>
+          <t>Yêu cầu hiển thị thực thể lặp lại</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18005,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Khôi phục nhân vật thử nghiệm chỉ có thể sử dụng trong khu vực thử nghiệm</t>
+          <t>Hồi phục nhân vật thử nghiệm chỉ có thể thực hiện trong khu vực thử nghiệm</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18075,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18145,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ "Falling Stars" để mở khóa</t>
+          <t>Hoàn thành Nhiệm vụ "Ngôi Sao Rơi" để mở khóa</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18215,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ "The Answer Is Where a River of Stars Falls" để mở khóa</t>
+          <t>Hoàn thành Nhiệm vụ "Đáp Án Nằm Nơi Dòng Sông Sao Rơi" để mở khóa</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18285,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 10</t>
+          <t>Đạt Cấp Độ Liên Minh 10</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18355,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 19</t>
+          <t>Đạt Cấp Độ Liên Minh 19</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18425,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18495,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ "Bạn Outshine the Fireworks" để mở khóa</t>
+          <t>Hoàn thành Nhiệm vụ "Ngươi Rực Rỡ Hơn Pháo Hoa" để mở khóa</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18565,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Hiển thị</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18635,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Replace</t>
+          <t>Thay thế</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18705,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Tính năng này bị vô hiệu hóa trong Chế độ Co-op</t>
+          <t>Tính năng này bị vô hiệu hóa trong Chế độ Đồng đội.</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18845,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Giai đoạn bị khóa</t>
+          <t>Sân khấu bị khóa.</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18915,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Chưa hoàn thành giai đoạn trước</t>
+          <t>Giai đoạn trước chưa hoàn thành</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18985,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Số bước hoàn thành không hợp lệ</t>
+          <t>Số lần xóa không hợp lệ</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19055,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Loại sự kiện không khớp</t>
+          <t>Loại sự kiện không tương thích</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19125,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Không tìm thấy dữ liệu trận đấu ban đầu</t>
+          <t>Không tìm thấy dữ liệu trận đấu ban đầu.</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19195,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Tính năng này bị vô hiệu hóa trong Chế độ Hợp tác</t>
+          <t>Tính năng này bị vô hiệu hóa trong Chế độ Đồng đội.</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19265,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Sự kiện không khả dụng</t>
+          <t>Sự kiện chưa khả dụng</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19405,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Bạn hiện không ở trong khu vực sự kiện</t>
+          <t>Hiện tại cậu không ở trong khu vực sự kiện</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19545,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Không thể chơi lá bài lúc này</t>
+          <t>Hiện không thể đánh bài</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19685,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình lá bài</t>
+          <t>Không tìm thấy cấu hình bài</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19755,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Lá bài này không có trong tay bạn</t>
+          <t>Thẻ này không có trong tay cậu</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19825,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Không thể chơi lá bài này</t>
+          <t>Không thể đánh lá bài này</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19965,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Phải chơi hết tất cả các cặp trước</t>
+          <t>Tất cả các cặp bài phải được đánh trước</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20035,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Lá bài đã chơi vi phạm luật chơi</t>
+          <t>Thẻ đã đánh vi phạm luật chơi</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20105,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Không thể rút bài lúc này</t>
+          <t>Hiện không thể rút bài</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20175,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Không thể chơi thêm lá bài</t>
+          <t>Không thể đánh thêm bài nữa</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20245,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Lá bài đã được chơi</t>
+          <t>Bài đã được sử dụng</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20315,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Đối thủ bị khóa</t>
+          <t>Đã khóa đối thủ</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20385,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Đối thủ trước bị khóa</t>
+          <t>Đối thủ trước đang bị khóa</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20455,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Đối thủ trước bị khóa</t>
+          <t>Đối thủ trước đang bị khóa</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20665,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Chưa hoàn thành nhiệm vụ trò chơi bài</t>
+          <t>Nhiệm vụ trò chơi bài chưa hoàn thành</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20735,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng trò chơi bài</t>
+          <t>Đã nhận phần thưởng trò chơi bài</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20805,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Không thể tham gia sự kiện này trong Chế độ Hợp tác</t>
+          <t>Không thể tham gia sự kiện này trong Chế Độ Đồng Đội</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20875,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Vào cabin Ginnungamere trong Nhiệm Vụ Chính "Ngôi Sao Du Hành Xa"</t>
+          <t>Vào cabin Ginnungamere trong Nhiệm Vụ Chính "Ngôi Sao Lang Thang Xa Xôi"</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20945,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Đến điểm xuất phát trong Nhiệm Vụ Chính "Ngôi Sao Du Hành Xa"</t>
+          <t>Quay lại điểm xuất phát trong Nhiệm Vụ Chính "Ngôi Sao Lang Thang Xa Xôi"</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21015,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Vào không gian làm việc bí mật trong Afterstory "Tất Cả Những Ánh Nắng Chạm Đến"</t>
+          <t>Vào xưởng làm việc bí mật trong Afterstory "Tất Cả Những Gì Ánh Mặt Trời Chạm Đến"</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21085,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương V Nhiệm Vụ Chính "Ánh Sao Từ Ngày Xưa" để mở khóa</t>
+          <t>Hoàn thành Chương V "Ánh Sao Từ Quá Khứ" của Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21155,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 5</t>
+          <t>Đạt Cấp Độ Liên Minh 5</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21225,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21365,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Dễ thôi</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21505,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Khó</t>
+          <t>Khó khăn</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21575,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Muse Dash</t>
+          <t>Vũ Điệu Cảm Hứng</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21645,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Adventures</t>
+          <t>Những Chuyến Phiêu Lưu</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21715,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Đạt Xếp hạng A trở lên trong bản nhạc này ở chế độ Thường để mở khóa</t>
+          <t>Đạt xếp hạng A trở lên trong bản nhạc này ở chế độ Normal để mở khóa</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21855,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Cài Đặt Điều Khiển</t>
+          <t>Thiết lập Điều khiển</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21925,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Interface Calibration</t>
+          <t>Hiệu Chỉnh Giao Diện</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21995,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Keybindings</t>
+          <t>Thiết Lập Phím Tắt</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22065,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Game Calibration</t>
+          <t>Hiệu Chuẩn Trò Chơi</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22135,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Offset</t>
+          <t>Độ lệch</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22205,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Đến Cài đặt</t>
+          <t>Vào Cài Đặt</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22275,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Sự kiện không khả dụng</t>
+          <t>Sự kiện chưa khả dụng</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22345,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Nhận được ít nhất 24 Crest trong bất kỳ giai đoạn nào của Tower of Adversity: Hazard Zone</t>
+          <t>Thu thập ít nhất 24 Huy Hiệu trong bất kỳ giai đoạn nào của Tháp Nghịch Cảnh: Khu Vực Nguy Hiểm</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22415,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Hoàn thành Afterstory "Lửa Đỏ Rực Từ Ngày Mai" để mở khóa</t>
+          <t>Hoàn thành Câu Chuyện Sau "Lửa Đỏ Rực Từ Ngày Mai" để mở khóa</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22485,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Endstate Matrix"</t>
+          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Ma Trận Kết Cục"</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22555,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương V Nhiệm Vụ Chính "Ánh Sao Từ Ngày Xưa" để mở khóa</t>
+          <t>Hoàn thành Chương V "Ánh Sao Từ Quá Khứ" của Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22625,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương V Nhiệm Vụ Chính "Ánh Sao Từ Ngày Xưa" để mở khóa</t>
+          <t>Hoàn thành Chương V "Ánh Sao Từ Quá Khứ" của Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22695,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Vui lòng hoàn thành Nhiệm Vụ Thám Hiểm "Vào Vùng Đất Nghịch Lý" trước</t>
+          <t>Hãy hoàn thành Nhiệm Vụ Thám Hiểm "Vào Vùng Đất Nghịch Lý" trước đã.</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22765,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 1.200 Spindrift</t>
+          <t>Thu thập tổng cộng 1.200 Bọt Sóng</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22835,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 2.200 Spindrift</t>
+          <t>Thu thập tổng cộng 2.200 Spindrift</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22905,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 3.000 Spindrift</t>
+          <t>Thu thập tổng cộng 3.000 Spindrift.</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22975,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 1.800 Spindrift</t>
+          <t>Thu thập tổng cộng 1.800 Spindrift</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23045,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Tiêu tổng cộng 2.000 Spindrift</t>
+          <t>Tổng cộng tiêu hao 2.000 Hoa Sóng</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23115,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23185,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23255,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23325,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23395,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 5.000 Spindrift</t>
+          <t>Thu thập tổng cộng 5.000 Bọt Sóng</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23465,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 để mở khóa</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23535,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Đạt 10.000 điểm trong Stability Accords để mở khóa</t>
+          <t>Đạt 10.000 điểm trong Hiệp Ước Ổn Định để mở khóa.</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23605,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn nhận rương Spacetrek Convoy Supply Chest</t>
+          <t>Đã đạt giới hạn nhận rương vật tư Đoàn vận tải Spacetrek</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23675,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Hoàn thành Afterstory "The Flaming Red from Tomorrow" để mở khóa</t>
+          <t>Hoàn thành Câu Chuyện Sau "Lửa Đỏ Rực Từ Ngày Mai" để mở khóa</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23745,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm Vụ Chính "Gold Suspended in Shadows"</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và hoàn thành Nhiệm Vụ Chính "Vàng Pha Bóng Tối"</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23885,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23955,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Gold Suspended in Shadows"</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Vàng Pha Bóng Tối"</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24025,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 8</t>
+          <t>Đạt Cấp Độ Liên Minh 8</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24095,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24165,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Cách mở khóa</t>
+          <t>Cách Mở Khóa</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24235,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm Vụ Chính "Gold Suspended in Shadows"</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và hoàn thành Nhiệm Vụ Chính "Vàng Pha Bóng Tối"</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24305,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24375,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24445,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24515,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24655,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24725,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24795,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Đang diễn ra</t>
+          <t>Đang tiếp tục</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24865,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Dễ thôi</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24935,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Khó</t>
+          <t>Khó khăn</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25005,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Hoàn thành Chế độ Thường để mở khóa Chế độ Khó</t>
+          <t>Hoàn thành Chế Độ Thường để mở khóa Chế Độ Khó</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25145,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Thu thập Huy chương</t>
+          <t>Thu thập Huy Chương</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25285,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi vượt qua Chế độ Dễ</t>
+          <t>Mở khóa sau khi hoàn thành Chế Độ Dễ</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25425,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Dọn thêm khối theo cách bạn thích để kiếm thêm điểm</t>
+          <t>Dọn nhiều khối cản trở theo cách của cậu để kiếm thêm điểm</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25495,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Nhân vật dùng thử không tồn tại</t>
+          <t>Nhân vật thử nghiệm không tồn tại</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25565,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Cách mở khóa</t>
+          <t>Cách Mở Khóa</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25635,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Soar to the Beat đã hết thời gian giới hạn</t>
+          <t>Sự kiện Bay Theo Nhịp đã hết thời gian giới hạn</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25705,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình nhiệm vụ Soar to the Beat</t>
+          <t>Không tìm thấy cấu hình nhiệm vụ cho sự kiện Bay Theo Nhịp</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25775,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình sự kiện Soar to the Beat</t>
+          <t>Không tìm thấy cấu hình sự kiện Bay Theo Nhịp</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25845,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình hành tinh Soar to the Beat</t>
+          <t>Không tìm thấy cấu hình hành tinh cho sự kiện Bay Theo Nhịp</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25915,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình giai đoạn Soar to the Beat</t>
+          <t>Không tìm thấy cấu hình giai đoạn cho sự kiện Bay Theo Nhịp</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25985,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình phân đoạn Soar to the Beat</t>
+          <t>Cấu hình phân đoạn "Bay Theo Nhịp" không tìm thấy</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26055,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình Resonator Soar to the Beat</t>
+          <t>Không tìm thấy cấu hình Resonator cho Bay theo Nhịp Điệu</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26125,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Lỗi tham số đầu vào Soar to the Beat</t>
+          <t>Lỗi tham số đầu vào sự kiện Bay Theo Nhịp</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26195,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Không tìm thấy dữ liệu sự kiện Soar to the Beat</t>
+          <t>Không tìm thấy dữ liệu sự kiện Bay Theo Nhịp</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26265,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Không thể nhận thưởng Soar to the Beat</t>
+          <t>Không thể nhận phần thưởng sự kiện Bay Theo Nhịp</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26335,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Soar to the Beat không khả dụng trong Chế độ Đồng đội</t>
+          <t>Sự kiện Bay Theo Nhịp không khả dụng trong Chế độ Đồng đội</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26405,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Giai đoạn Soar to the Beat chưa mở</t>
+          <t>Sân khấu Soar to the Beat chưa mở</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26475,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Chưa hoàn thành giai đoạn tiên quyết của Soar to the Beat</t>
+          <t>Chưa hoàn thành giai đoạn tiên quyết của sự kiện Bay Theo Nhịp</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26545,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Giai đoạn Soar to the Beat chưa mở</t>
+          <t>Giai đoạn "Bay Theo Nhịp" chưa khả dụng</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26615,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Hành tinh Soar to the Beat chưa mở</t>
+          <t>Hành tinh của sự kiện Bay Theo Nhịp không khả dụng</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26685,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Resonator Soar to the Beat chưa mở</t>
+          <t>Resonator Bay theo Nhịp Điệu không khả dụng</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26755,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Sự kiện Soar to the Beat không khớp</t>
+          <t>Sự kiện Bay Theo Nhịp không khớp</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26825,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Payload không hợp lệ</t>
+          <t>Dữ liệu tải không hợp lệ</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26965,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Không có Companion Resonator khả dụng</t>
+          <t>Chưa có Resonator đồng hành</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27105,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Loại thử thách không khớp</t>
+          <t>Không khớp loại thách đấu</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27245,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Chưa chọn Companion Resonator cho Soar to the Beat</t>
+          <t>Đã chọn mạng lưới đồng hành Bay theo Nhịp Điệu</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27315,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Thiếu dữ liệu trận đấu Soar to the Beat</t>
+          <t>Dữ liệu chiến đấu Bay theo Nhịp Điệu bị thiếu</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -28225,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28435,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Không thể tương tác với Resonator đã bị hạ gục</t>
+          <t>Bạn không thể tương tác với Resonator đã bị hạ gục.</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28505,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Bountiful Waves hiện không khả dụng</t>
+          <t>Sóng Dạt Dào hiện không khả dụng</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28575,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Nhiệm vụ Bountiful Waves chưa hoàn thành</t>
+          <t>Nhiệm vụ Sóng Dạt Dào chưa hoàn thành</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28645,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng nhiệm vụ Bountiful Waves</t>
+          <t>Phần thưởng nhiệm vụ Sóng Dạt Dào đã nhận rồi</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28715,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Dữ liệu phân đoạn Soar to the Beat không khớp</t>
+          <t>Dữ liệu phân đoạn "Bay Theo Nhịp" không khớp</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28785,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28855,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Mở khóa sau 10:00 ngày 30 tháng 4 (UTC+8)</t>
+          <t>Mở sau 10:00 ngày 30/4 (UTC+8)</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28925,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Mở khóa sau 10:00 ngày 23 tháng 5 (UTC+8)</t>
+          <t>Mở sau 10:00 ngày 23/5 (UTC+8)</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28995,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Không thể tham gia sự kiện này trong Chế độ Co-Op</t>
+          <t>Không thể tham gia sự kiện này trong Chế Độ Đồng Đội</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29065,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29135,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29275,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Chính "Starlights from Yesterdays"</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Ánh Sao Từ Những Ngày Xưa"</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29485,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Trong sự kiện, đạt 200 Điểm Hoạt động Sổ Tay Hướng Dẫn</t>
+          <t>Trong sự kiện, thu thập 200 Điểm Hoạt Động Sổ Tay Hướng Dẫn.</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29555,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Trong sự kiện, đạt 500 Điểm Hoạt động Sổ Tay Hướng Dẫn</t>
+          <t>Trong sự kiện, thu thập 500 Điểm Hoạt Động Sổ Tay Hướng Dẫn.</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29625,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Trong sự kiện, đạt 1.000 Điểm Hoạt động Sổ Tay Hướng Dẫn</t>
+          <t>Trong sự kiện, thu thập 1.000 Điểm Hoạt Động Sổ Tay Hướng Dẫn.</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29695,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Trong sự kiện, nhận được 1.500 Điểm Hoạt Động Sổ Tay Hướng Dẫn</t>
+          <t>Trong sự kiện, thu thập 1.500 Điểm Hoạt Động Sổ Tay Hướng Dẫn.</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29765,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Đạt 200 Tiến Độ Cá Nhân trong Second Coming of Solaris: Collab Season</t>
+          <t>Đạt 200 Tiến Độ Cá Nhân trong Sự Kiện Second Coming of Solaris: Collab Season</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29835,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Đạt 400 Tiến Độ Cá Nhân trong Second Coming of Solaris: Collab Season</t>
+          <t>Đạt 400 Tiến Độ Cá Nhân trong Sự Trở Lại Của Solaris: Mùa Cộng Tác</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29975,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Đạt 800 Tiến Độ Cá Nhân trong Second Coming of Solaris: Collab Season</t>
+          <t>Đạt 800 Tiến Độ Cá Nhân trong Sự Trở Lại Của Solaris: Mùa Cộng Tác</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30045,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Beneath a Melting Night Sky"</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Dưới Bầu Trời Đêm Tan Chảy"</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30115,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 6 Mô-đun Mở Rộng Chiến Thuật Trên Không</t>
+          <t>Thu thập tổng cộng 6 Mô-đun Mở Rộng Chiến Thuật Hàng Không</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30185,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Nhận được 4.000 Mẫu Ảo trong "Depths of Illusive Realm: Chromatic Fantasy"</t>
+          <t>Thu thập 4.000 Mẫu Vật Ảo trong "Vực Sâu Ảo Ảnh: Ảo Giác Sắc Màu"</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30255,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Nhận được 6.000 Mẫu Ảo trong "Depths of Illusive Realm: Chromatic Fantasy"</t>
+          <t>Thu thập 6.000 Mẫu Vật Ảo trong "Vực Sâu Ảo Ảnh: Ảo Giác Ngũ Sắc"</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30325,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Trong sự kiện, nhận được 200 Điểm Hoạt Động Sổ Tay Hướng Dẫn</t>
+          <t>Trong sự kiện, thu thập 200 Điểm Hoạt Động Sổ Tay Hướng Dẫn.</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30395,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Trong sự kiện, nhận được 500 Điểm Hoạt Động Sổ Tay Hướng Dẫn</t>
+          <t>Trong sự kiện, thu thập 500 Điểm Hoạt Động Sổ Tay Hướng Dẫn.</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30465,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Trong sự kiện, nhận được 1.000 Điểm Hoạt Động Sổ Tay Hướng Dẫn</t>
+          <t>Trong sự kiện, thu thập 1.000 Điểm Hoạt Động Sổ Tay Hướng Dẫn.</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30535,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Trong sự kiện, nhận được 1.500 Điểm Hoạt Động Sổ Tay Hướng Dẫn</t>
+          <t>Trong sự kiện, thu thập 1.500 Điểm Hoạt Động Sổ Tay Hướng Dẫn.</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30605,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Đạt 25% Tiến Độ Thám Hiểm ở 1 khu vực của Roya Frostlands: Dimmr Plains</t>
+          <t>Đạt 25% Tiến Độ Thám Hiểm ở 1 khu vực thuộc Roya Frostlands: Dimmr Plains</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30675,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Đạt 25% Tiến Độ Thám Hiểm ở 2 khu vực của Roya Frostlands: Dimmr Plains</t>
+          <t>Đạt 25% Tiến Độ Thám Hiểm ở 2 khu vực thuộc Roya Frostlands: Dimmr Plains</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30745,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Đạt 50% Tiến Độ Thám Hiểm ở 3 khu vực của Roya Frostlands: Dimmr Plains</t>
+          <t>Hoàn thành 50% Tiến Độ Thám Hiểm ở 3 khu vực thuộc Roya Frostlands: Dimmr Plains</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30815,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Đạt 50% Tiến Độ Thám Hiểm ở 4 khu vực của Roya Frostlands: Dimmr Plains</t>
+          <t>Hoàn thành 50% Tiến Độ Thám Hiểm ở 4 khu vực thuộc Roya Frostlands: Dimmr Plains</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30885,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -31025,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình phần thưởng chu kỳ</t>
+          <t>Không tìm thấy cấu hình phần thưởng Chu Kỳ</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31095,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình chu kỳ</t>
+          <t>Không tìm thấy cấu hình Chu Kỳ</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31165,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Không trong khoảng thời gian hợp lệ của chu kỳ</t>
+          <t>Không trong chu kỳ hiệu lực</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31235,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Đã nhận phần thưởng chu kỳ</t>
+          <t>Phần thưởng Chu Kỳ đã nhận</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31305,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Phần thưởng chu kỳ trống</t>
+          <t>Phần thưởng chu kỳ trống rỗng</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31585,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Hết thời gian nhận thưởng chu kỳ</t>
+          <t>Hết thời gian nhận thưởng Chu Kỳ</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31655,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31725,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Thử thách lại</t>
+          <t>Thử Thách Lại</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31795,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Thường Mode</t>
+          <t>Chế Độ Thường</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31865,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Infinite Mode</t>
+          <t>Chế Độ Vô Tận</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31935,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>"Bountiful Waves" event</t>
+          <t>"Sự kiện \"Sóng Phì Nhiêu\""</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32005,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>"Second Coming of Solaris: Collab Season" event</t>
+          <t>"Sự kiện “Solaris Trở Lại: Mùa Cộng Tác”"</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32075,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>2026 Birthday Blessing</t>
+          <t>Lời Chúc Mừng Sinh Nhật 2026</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32145,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Currently Unavailable</t>
+          <t>Hiện không khả dụng</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32215,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Nhiệm vụ chính "What Yesterday Wept, Hôm nay Doth Sing"</t>
+          <t>Nhiệm vụ chính "Điều hôm qua khóc, hôm nay hát"</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32285,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>2025 Birthday Blessing</t>
+          <t>Lời Chúc Mừng Sinh Nhật 2025</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32425,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Xbox ID</t>
+          <t>ID Xbox</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32495,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Lưu ý: Bạn đang ở chế độ cross-play</t>
+          <t>Thông báo: Bạn đang ở chế độ chơi chéo</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32565,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Chỉ bạn bè trên PSN</t>
+          <t>Chỉ Bạn Bè Trên PSN</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32635,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Chỉ bạn bè trên Xbox</t>
+          <t>Bạn bè trên Xbox thôi mà</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32705,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Không có bạn bè khả dụng</t>
+          <t>Không có bạn bè trực tuyến</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32845,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Chưa có dữ liệu Xếp hạng</t>
+          <t>Chưa có dữ liệu xếp hạng</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32985,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Thiếu cấu hình Nhiệm vụ/Nhiệm vụ phụ</t>
+          <t>Thiếu cấu hình nhiệm vụ/nhiệm vụ phụ</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33055,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Cấu hình sự kiện không khớp</t>
+          <t>Cấu hình sự kiện không khớp.</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33125,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33195,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Nhiệm vụ/chưa hoàn thành</t>
+          <t>Nhiệm vụ/nhiệm vụ phụ chưa hoàn thành</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33265,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Cấu hình rơi vật phẩm bất thường</t>
+          <t>Cấu hình thả bất thường</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33335,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng nhiều lần</t>
+          <t>Nhận phần thưởng trùng lặp</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33545,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình Resonator</t>
+          <t>Không tìm thấy cấu hình Resonator.</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33615,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Chưa sở hữu Resonator</t>
+          <t>Chưa sở hữu Resonator này</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33685,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Lấy cấp độ tối đa thất bại</t>
+          <t>Đã đạt cấp độ tối đa</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33755,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Đã vượt cấp tối đa của Resonator</t>
+          <t>Đã vượt quá Cấp Resonator tối đa</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33965,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Không thể nhận Trial Resonators</t>
+          <t>Không thể nhận Resonator Thử Nghiệm</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34035,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Không tìm thấy dữ liệu Vũ khí</t>
+          <t>Không tìm thấy dữ liệu Vũ Khí</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34105,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình Vũ khí</t>
+          <t>Không tìm thấy cấu hình Vũ Khí</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34175,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Không tìm thấy dữ liệu Resonator</t>
+          <t>Không tìm thấy dữ liệu Resonator.</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34245,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình Resonator</t>
+          <t>Không tìm thấy cấu hình Resonator.</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34315,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Không thể trang bị loại vũ khí này</t>
+          <t>Không thể trang bị loại vũ khí này.</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34385,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Không thể chuyển đổi Signature Weapon</t>
+          <t>Không thể chuyển đổi Vũ Khí Đặc Trưng</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34455,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Đã trang bị trùng lặp</t>
+          <t>Trang bị lại nhiều lần</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34525,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Số lượng phân giải không hợp lệ</t>
+          <t>Số lượng giải mã không hợp lệ</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34595,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Đã phân giải trùng lặp</t>
+          <t>Giải mã lại</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34665,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Không có vũ khí để phân giải</t>
+          <t>Không có vũ khí để giải mã</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34735,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Khởi tạo Vũ khí thất bại</t>
+          <t>Khởi tạo vũ khí thất bại</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34805,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Không có bạn bè nào</t>
+          <t>Không có bạn bè trực tuyến</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34945,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Cấp độ bị khóa</t>
+          <t>Sân khấu bị khóa.</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35015,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Thử thách hàng ngày không chính xác</t>
+          <t>Thể thức thử thách hàng ngày không chính xác</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35155,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Thử thách hàng ngày không khả dụng</t>
+          <t>Thử thách hằng ngày chưa mở</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35225,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Signature Weapon không khớp</t>
+          <t>Vũ khí không tương thích</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35295,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Hoàn thành Taoyuan Vale 4 để mở khóa</t>
+          <t>Hoàn thành Thung Lũng Taoyuan 4 để mở khóa</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35365,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Hoàn thành Ragunna 4 để mở khóa</t>
+          <t>Đánh bại Ragunna 4 lần để mở khóa</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
